--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$21</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,6 +438,9 @@
   </si>
   <si>
     <t>http://hl7.org/cda/stds/core/ValueSet/CDARoleCode</t>
+  </si>
+  <si>
+    <t>ParticipantRole.sdtcSpecialty</t>
   </si>
   <si>
     <t>ParticipantRole.addr</t>
@@ -804,7 +807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.18359375" customWidth="true" bestFit="true"/>
@@ -2374,7 +2377,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>137</v>
       </c>
@@ -2393,7 +2396,7 @@
         <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>74</v>
@@ -2402,11 +2405,9 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2477,10 +2478,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2503,10 +2504,10 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -2558,7 +2559,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2578,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2592,7 +2593,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>96</v>
@@ -2604,10 +2605,10 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -2659,13 +2660,13 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>74</v>
@@ -2679,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2705,10 +2706,10 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -2760,7 +2761,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2780,10 +2781,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2806,10 +2807,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2861,7 +2862,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2879,8 +2880,109 @@
         <v>74</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK20">
+  <autoFilter ref="A1:AK21">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -2890,7 +2992,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI19">
+  <conditionalFormatting sqref="A2:AI20">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-participant-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
